--- a/Source/Варианты.xlsx
+++ b/Source/Варианты.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\python projects repos\python-exam-django\Source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk\Мои материалы\2 курс\ОАП\Раздел 5 DJANGO\python-exam-django-2levels\Source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94496916-2F19-4035-A942-A78EE8D73BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8072049-DAA3-4982-971C-F13F369CFC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9F74F613-58DA-413B-83E7-BEA6893693A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F74F613-58DA-413B-83E7-BEA6893693A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="Варианты">Лист1!$A$3:$E$51</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="75">
   <si>
     <t>Название базы данных</t>
   </si>
@@ -42,23 +45,9 @@
     <t>Номер варианта</t>
   </si>
   <si>
-    <t>Создать 
-Панель администратора</t>
-  </si>
-  <si>
-    <t>+</t>
-  </si>
-  <si>
-    <t>Создать 
-Дополнительную страницу</t>
-  </si>
-  <si>
     <t>Вид дополнительной страницы</t>
   </si>
   <si>
-    <t>Дополнительные Указания</t>
-  </si>
-  <si>
     <t xml:space="preserve">ВАРИАНТЫ ДЛЯ ЭКЗАМЕНА </t>
   </si>
   <si>
@@ -68,63 +57,33 @@
     <t>сотрудники старше 40 лет</t>
   </si>
   <si>
-    <t>на всех  страницах сделать футер с данными компании:  Название, телефон, email</t>
-  </si>
-  <si>
     <t>car_park</t>
   </si>
   <si>
-    <t xml:space="preserve">только японские марки </t>
-  </si>
-  <si>
     <t>library</t>
   </si>
   <si>
     <t>публикации после 1879 года</t>
   </si>
   <si>
-    <t>нет</t>
-  </si>
-  <si>
     <t xml:space="preserve">warehouse </t>
   </si>
   <si>
     <t>товары с ценой от 20 тыс.руб. до 30 тыс.руб.</t>
   </si>
   <si>
-    <t>Сделать дополнительный столбец с кнопкой "купить" в каждой строке таблицы</t>
-  </si>
-  <si>
     <t>zoo</t>
   </si>
   <si>
-    <t>страница с одним животным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ссылку на страницу одного животного создать внутри таблицы в поле name </t>
-  </si>
-  <si>
     <t>medical_clinic</t>
   </si>
   <si>
-    <t>пациенты старше  40 лет</t>
-  </si>
-  <si>
-    <t>Данные последнего столбца вывести в зеленом цвете</t>
-  </si>
-  <si>
-    <t>Данные последнего столбца вывести в синем цвете</t>
-  </si>
-  <si>
     <t>music_school</t>
   </si>
   <si>
     <t>только студенты по классу фортепиано</t>
   </si>
   <si>
-    <t>на всех  страницах сделать футер с данными музыкальной школы:  Название, телефон, email</t>
-  </si>
-  <si>
     <t>restaurant</t>
   </si>
   <si>
@@ -140,39 +99,18 @@
     <t>bookstore</t>
   </si>
   <si>
-    <t>товары с ценой от 300 руб. до 400 руб. включительно</t>
-  </si>
-  <si>
-    <t>на всех  страницах сделать футер с данными магазина:  Название, телефон, email</t>
-  </si>
-  <si>
     <t>fitness_center</t>
   </si>
   <si>
-    <t>страница с одним клиентом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ссылку на страницу одного клиента создать внутри таблицы в поле name </t>
-  </si>
-  <si>
     <t>car_service</t>
   </si>
   <si>
     <t>только февральские ремонты</t>
   </si>
   <si>
-    <t>Данные последнего столбца вывести в красном цвете</t>
-  </si>
-  <si>
     <t>art_gallery</t>
   </si>
   <si>
-    <t>страница с одним художественным произведением</t>
-  </si>
-  <si>
-    <t>ссылку на страницу одного протизведения создать внутри таблицы в поле title</t>
-  </si>
-  <si>
     <t>cinema</t>
   </si>
   <si>
@@ -188,7 +126,144 @@
     <t>publishing_house</t>
   </si>
   <si>
-    <t>публикации 20 века</t>
+    <t xml:space="preserve">Элемент перехода на панель администратора и дополнительную страницу </t>
+  </si>
+  <si>
+    <t>Дополнительное оформление сайта</t>
+  </si>
+  <si>
+    <t>кнопки внизу видимого экрана</t>
+  </si>
+  <si>
+    <t>кнопки на  боковой панели</t>
+  </si>
+  <si>
+    <t>элементы header</t>
+  </si>
+  <si>
+    <t>данные в виде карточек отдельных предметов (без таблицы)</t>
+  </si>
+  <si>
+    <t>светлая тема, 
+сделать дополнительный столбец с кнопкой "купить" в каждой строке таблицы</t>
+  </si>
+  <si>
+    <t>темная тема, 
+сделать дополнительный столбец с кнопкой "купить" в каждой строке таблицы</t>
+  </si>
+  <si>
+    <t>только разработчики и рекрутеры</t>
+  </si>
+  <si>
+    <t>только сотрудники с третьего этажа</t>
+  </si>
+  <si>
+    <t>только ремонты со словом "замена"</t>
+  </si>
+  <si>
+    <t>только  ремонты машин Toyota, Mazda, Honda и Nissan</t>
+  </si>
+  <si>
+    <t>только японские марки (Toyota, Honda и Nissan)</t>
+  </si>
+  <si>
+    <t>машины после 2020 года выпуска</t>
+  </si>
+  <si>
+    <t>автомобили владельца с id=2</t>
+  </si>
+  <si>
+    <t>только книги с четным количеством страниц</t>
+  </si>
+  <si>
+    <t>только Романы</t>
+  </si>
+  <si>
+    <t>только бытовая техника</t>
+  </si>
+  <si>
+    <t>товары полученные в январе 2025 года</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выборка по этому условию: имя животного начинается на букву "Л" </t>
+  </si>
+  <si>
+    <t>Животные старше 6 лет</t>
+  </si>
+  <si>
+    <t>Животные с хорошим и отличным здоровьем</t>
+  </si>
+  <si>
+    <t>пациенты женщины старше  40 лет</t>
+  </si>
+  <si>
+    <t>пациенты родившиеся в марте</t>
+  </si>
+  <si>
+    <t>пациенты мужчины лечащиеся у терапевта</t>
+  </si>
+  <si>
+    <t>только студенты с четной датой рождения</t>
+  </si>
+  <si>
+    <t>только ученики Ольги Кузнецовой</t>
+  </si>
+  <si>
+    <t>только  блюда  больше 400 и меньше 500 руб включительно</t>
+  </si>
+  <si>
+    <t>только блюда начинающиеся на букву "П"</t>
+  </si>
+  <si>
+    <t>туры летом</t>
+  </si>
+  <si>
+    <t>туры в цене от 80 тыс.руб. до 95 тыс.руб включительно</t>
+  </si>
+  <si>
+    <t>название произведения содержит две буквы "Н"</t>
+  </si>
+  <si>
+    <t>Романы  20 века</t>
+  </si>
+  <si>
+    <t>посетители у тренера Марии Ивановой</t>
+  </si>
+  <si>
+    <t>только Кардио и Йога</t>
+  </si>
+  <si>
+    <t>у кого посещение  летом</t>
+  </si>
+  <si>
+    <t>Романы с ценой от 300 руб. до 400 руб. включительно</t>
+  </si>
+  <si>
+    <t>Романы Михаила Булгакова</t>
+  </si>
+  <si>
+    <t>В названии книги содержится две и более буквы "А"</t>
+  </si>
+  <si>
+    <t>кино  в  19:00</t>
+  </si>
+  <si>
+    <t>все сеансы Интерстеллар</t>
+  </si>
+  <si>
+    <t>продажи в феврале</t>
+  </si>
+  <si>
+    <t>Продали Елене, Наталье и Дмитрию</t>
+  </si>
+  <si>
+    <t>картины 20 века</t>
+  </si>
+  <si>
+    <t>картины французских живописцев</t>
+  </si>
+  <si>
+    <t>название произведения содержит две и более буквы "и"</t>
   </si>
 </sst>
 </file>
@@ -214,7 +289,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -230,6 +305,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -261,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -269,19 +380,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -598,370 +736,898 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D26A3550-BEE6-4E25-91D6-6C32BB9E4678}">
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr defaultColWidth="3.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" customWidth="1"/>
-    <col min="6" max="6" width="68.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="3" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="C5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="E12" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="F13"/>
+    </row>
+    <row r="14" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="F14"/>
+    </row>
+    <row r="15" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="D20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>18</v>
       </c>
+      <c r="B21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="1:6" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>27</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>29</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="1:6" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>31</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>32</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>33</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37"/>
+    </row>
+    <row r="38" spans="1:6" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38"/>
+    </row>
+    <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>36</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>37</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40"/>
+    </row>
+    <row r="41" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>38</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F41"/>
+    </row>
+    <row r="42" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>39</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>40</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>41</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>42</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>43</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>44</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>45</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48"/>
+    </row>
+    <row r="49" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>46</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F49"/>
+    </row>
+    <row r="50" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>47</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50"/>
+    </row>
+    <row r="51" spans="1:6" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>48</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F51"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F51">
+    <sortCondition ref="F4:F51"/>
+  </sortState>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Source/Варианты.xlsx
+++ b/Source/Варианты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk\Мои материалы\2 курс\ОАП\Раздел 5 DJANGO\python-exam-django-2levels\Source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8072049-DAA3-4982-971C-F13F369CFC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F13A62-218F-459B-822C-B628D6AB1DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F74F613-58DA-413B-83E7-BEA6893693A6}"/>
   </bookViews>
@@ -372,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -386,40 +386,46 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -742,19 +748,19 @@
     <col min="1" max="1" width="9.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.33203125" style="7" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -763,7 +769,7 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -774,16 +780,16 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="12" t="s">
@@ -791,33 +797,33 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="9">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="9">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="14" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="12" t="s">
@@ -825,123 +831,123 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="9">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="13" t="s">
+      <c r="D7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="9">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="14" t="s">
+      <c r="D8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="9">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="9">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="13" t="s">
+      <c r="D10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="A11" s="9">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="9">
         <v>9</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="A13" s="9">
         <v>10</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="14" t="s">
         <v>31</v>
       </c>
       <c r="E13" s="12" t="s">
@@ -950,52 +956,52 @@
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="A14" s="9">
         <v>11</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="13" t="s">
+      <c r="D14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="A15" s="9">
         <v>12</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="A16" s="9">
         <v>13</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="17" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="12" t="s">
@@ -1004,34 +1010,34 @@
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="A17" s="9">
         <v>14</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="13" t="s">
+      <c r="D17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="A18" s="9">
         <v>15</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -1039,102 +1045,102 @@
       </c>
     </row>
     <row r="19" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="A19" s="9">
         <v>16</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="A20" s="9">
         <v>17</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="D20" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+    <row r="21" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9">
         <v>18</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="13" t="s">
+      <c r="D21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="A22" s="9">
         <v>19</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="A23" s="9">
         <v>20</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+      <c r="A24" s="9">
         <v>21</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="17" t="s">
         <v>32</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -1143,16 +1149,16 @@
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+      <c r="A25" s="9">
         <v>22</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="17" t="s">
         <v>32</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -1161,16 +1167,16 @@
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+      <c r="A26" s="9">
         <v>23</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -1179,52 +1185,52 @@
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+      <c r="A27" s="9">
         <v>24</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+      <c r="A28" s="9">
         <v>25</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+      <c r="A29" s="9">
         <v>26</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -1233,52 +1239,52 @@
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+      <c r="A30" s="9">
         <v>27</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="14" t="s">
+      <c r="D30" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+      <c r="A31" s="9">
         <v>28</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F31"/>
     </row>
     <row r="32" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+      <c r="A32" s="9">
         <v>29</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="14" t="s">
         <v>31</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -1287,34 +1293,34 @@
       <c r="F32"/>
     </row>
     <row r="33" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+      <c r="A33" s="9">
         <v>30</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="14" t="s">
+      <c r="D33" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F33"/>
     </row>
     <row r="34" spans="1:6" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
+      <c r="A34" s="9">
         <v>31</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="14" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="12" t="s">
@@ -1323,70 +1329,70 @@
       <c r="F34"/>
     </row>
     <row r="35" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+      <c r="A35" s="9">
         <v>32</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F35"/>
     </row>
     <row r="36" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>33</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="A36" s="9">
+        <v>33</v>
+      </c>
+      <c r="B36" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F36"/>
     </row>
     <row r="37" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+      <c r="A37" s="9">
         <v>34</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F37"/>
     </row>
     <row r="38" spans="1:6" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+      <c r="A38" s="9">
         <v>35</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="17" t="s">
         <v>32</v>
       </c>
       <c r="E38" s="12" t="s">
@@ -1395,69 +1401,69 @@
       <c r="F38"/>
     </row>
     <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+      <c r="A39" s="9">
         <v>36</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+      <c r="A40" s="9">
         <v>37</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F40"/>
     </row>
     <row r="41" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+      <c r="A41" s="9">
         <v>38</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F41"/>
     </row>
     <row r="42" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+      <c r="A42" s="9">
         <v>39</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -1466,50 +1472,50 @@
       <c r="F42"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+      <c r="A43" s="9">
         <v>40</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+      <c r="A44" s="9">
         <v>41</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+      <c r="A45" s="9">
         <v>42</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="14" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -1517,33 +1523,33 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+      <c r="A46" s="9">
         <v>43</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" s="14" t="s">
+      <c r="D46" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
+      <c r="A47" s="9">
         <v>44</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -1551,52 +1557,52 @@
       </c>
     </row>
     <row r="48" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
+      <c r="A48" s="9">
         <v>45</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="16" t="s">
         <v>35</v>
       </c>
       <c r="F48"/>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+      <c r="A49" s="9">
         <v>46</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F49"/>
     </row>
     <row r="50" spans="1:6" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+      <c r="A50" s="9">
         <v>47</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="17" t="s">
         <v>32</v>
       </c>
       <c r="E50" s="12" t="s">
@@ -1604,20 +1610,20 @@
       </c>
       <c r="F50"/>
     </row>
-    <row r="51" spans="1:6" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+    <row r="51" spans="1:6" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="9">
         <v>48</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E51" s="14" t="s">
+      <c r="D51" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F51"/>
